--- a/功能验收核对清单.xlsx
+++ b/功能验收核对清单.xlsx
@@ -2164,7 +2164,7 @@
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>生成时间：2026-06-05 21:37:16 | 基于原始需求文档</t>
+          <t>生成时间：2026-06-05 23:54:01 | 基于原始需求文档</t>
         </is>
       </c>
     </row>
